--- a/src/assets/files/catalog.xlsx
+++ b/src/assets/files/catalog.xlsx
@@ -32,9 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -65,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,910 +397,823 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I28"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="str">
+      <c r="A1" t="str">
         <v>INDEX</v>
       </c>
-      <c r="B1" s="1" t="str">
+      <c r="B1" t="str">
         <v>PROJECT NAME</v>
       </c>
-      <c r="C1" s="1" t="str">
+      <c r="C1" t="str">
         <v>PROJECT ID</v>
       </c>
-      <c r="D1" s="1" t="str">
+      <c r="D1" t="str">
         <v>ARCHITECT</v>
       </c>
-      <c r="E1" s="1" t="str">
+      <c r="E1" t="str">
         <v>SERVICE PERFORMED</v>
       </c>
-      <c r="F1" s="1" t="str">
+      <c r="F1" t="str">
         <v>LOCATION</v>
       </c>
-      <c r="G1" s="1" t="str">
+      <c r="G1" t="str">
         <v>CATEGORY</v>
       </c>
-      <c r="H1" s="1" t="str">
+      <c r="H1" t="str">
         <v>LINK</v>
       </c>
-      <c r="I1" s="1" t="str">
+      <c r="I1" t="str">
         <v>COVER IMAGE</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="str">
+      <c r="B2" t="str">
         <v>SMART BUILDING-TOWER 3</v>
       </c>
-      <c r="C2" s="1" t="str">
+      <c r="C2" t="str">
         <v>smart-building-tower-3</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" t="str">
         <v>GINARD Studio</v>
       </c>
-      <c r="E2" s="1" t="str">
-        <v>Structural engineering services for a 23-story apartment building with approximately 160,000 SF, including 7-story parking garages and a pool.</v>
-      </c>
-      <c r="F2" s="1" t="str">
+      <c r="E2" t="str">
+        <v>Structural engineering services for a 23-story apartment building with approximately 160,000 SF, including 7-story parking garages and a pool. The building structure consist of concrete framing with shear walls and post tension slabs.</v>
+      </c>
+      <c r="F2" t="str">
         <v>Miami, FL</v>
       </c>
-      <c r="G2" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H2" s="1" t="str">
+      <c r="G2" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H2" t="str">
         <v>08-Pictures/SMART BUILDING-TOWER 3</v>
       </c>
-      <c r="I2" s="1" t="str">
+      <c r="I2" t="str">
         <v>Picture1.webp</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="str">
+      <c r="B3" t="str">
         <v>SMART BUILDING-TOWER 1 &amp; 2</v>
       </c>
-      <c r="C3" s="1" t="str">
+      <c r="C3" t="str">
         <v>smart-building-tower-1-and-2</v>
       </c>
-      <c r="D3" s="1" t="str">
+      <c r="D3" t="str">
         <v>Hernando Carrillo Architect</v>
       </c>
-      <c r="E3" s="1" t="str">
+      <c r="E3" t="str">
         <v>Structural design engineering services for two 23-story apartment buildings with approximately 140,000 SF each, including 7-story parking garages and a pool.</v>
       </c>
-      <c r="F3" s="1" t="str">
+      <c r="F3" t="str">
         <v>Miami, FL</v>
       </c>
-      <c r="G3" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H3" s="1" t="str">
+      <c r="G3" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H3" t="str">
         <v>08-Pictures/SMART BUIDING-TOWER 1 &amp; 2</v>
       </c>
-      <c r="I3" s="1" t="str">
+      <c r="I3" t="str">
         <v>Picture2.webp</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="str">
+      <c r="B4" t="str">
         <v>FOUNTAINBLEAU</v>
       </c>
-      <c r="C4" s="1" t="str">
+      <c r="C4" t="str">
         <v>fountainbleau</v>
       </c>
-      <c r="D4" s="1" t="str">
+      <c r="D4" t="str">
         <v>Valle Valle and Partners</v>
       </c>
-      <c r="E4" s="1" t="str">
+      <c r="E4" t="str">
         <v>Structural design engineering services for a Six-story apartment building with an approximate square footage of 160,000 SF, including 3-story parking garages.</v>
       </c>
-      <c r="F4" s="1" t="str">
+      <c r="F4" t="str">
         <v>Miami, FL</v>
       </c>
-      <c r="G4" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H4" s="1" t="str">
+      <c r="G4" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H4" t="str">
         <v>08-Pictures/FOUNTAINBLEAU</v>
       </c>
-      <c r="I4" s="1" t="str">
+      <c r="I4" t="str">
         <v>Picture4.webp</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="str">
+      <c r="B5" t="str">
         <v>UNIVERSAL STUDIOS- HOW TO TRAIN YOUR DRAGON</v>
       </c>
-      <c r="C5" s="1" t="str">
+      <c r="C5" t="str">
         <v>universal-studios-how-to-train-your-dragon</v>
       </c>
-      <c r="D5" s="1" t="str">
+      <c r="D5" t="str">
         <v>Forrec</v>
       </c>
-      <c r="E5" s="1" t="str">
-        <v>Structural design engineering services for a new amusement park in Orlando, Florida.</v>
-      </c>
-      <c r="F5" s="1" t="str">
+      <c r="E5" t="str">
+        <v>Review Structural design engineering services for a new amusement park in Orlando, Florida.</v>
+      </c>
+      <c r="F5" t="str">
         <v>Orlando, FL</v>
       </c>
-      <c r="G5" s="1" t="str">
+      <c r="G5" t="str">
         <v>PARK &amp; AMUSEMENT</v>
       </c>
-      <c r="H5" s="1" t="str">
+      <c r="H5" t="str">
         <v>08-Pictures/UNIVERSAL STUDIO</v>
       </c>
-      <c r="I5" s="1" t="str">
+      <c r="I5" t="str">
         <v>Picture5.webp</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="str">
+      <c r="B6" t="str">
         <v>DELMAR</v>
       </c>
-      <c r="C6" s="1" t="str">
+      <c r="C6" t="str">
         <v>delmar</v>
       </c>
-      <c r="D6" s="1" t="str">
+      <c r="D6" t="str">
         <v>Corwil Architects</v>
       </c>
-      <c r="E6" s="1" t="str">
+      <c r="E6" t="str">
         <v>Structural design engineering and threshold services for a Twelve-story apartment building, including a 3-story parking garage.</v>
       </c>
-      <c r="F6" s="1" t="str">
+      <c r="F6" t="str">
         <v>St. Petersburg, FL</v>
       </c>
-      <c r="G6" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H6" s="1" t="str">
+      <c r="G6" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H6" t="str">
         <v>08-Pictures/DELMAR</v>
       </c>
-      <c r="I6" s="1" t="str">
+      <c r="I6" t="str">
         <v>Picture4.webp</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="str">
+      <c r="B7" t="str">
         <v>CASA GLASS OAK</v>
       </c>
-      <c r="C7" s="1" t="str">
+      <c r="C7" t="str">
         <v>casa-glass-oak</v>
       </c>
-      <c r="D7" s="1" t="str">
+      <c r="D7" t="str">
         <v>FAO Architects</v>
       </c>
-      <c r="E7" s="1" t="str">
-        <v>Structural design engineering services for a 2-story custom home.</v>
-      </c>
-      <c r="F7" s="1" t="str">
+      <c r="E7" t="str">
+        <v>Structural and civil design engineering services for a 2-story custom home.</v>
+      </c>
+      <c r="F7" t="str">
         <v>Coral Gables, FL</v>
       </c>
-      <c r="G7" s="1" t="str">
+      <c r="G7" t="str">
         <v>SINGLE FAMILY</v>
       </c>
-      <c r="H7" s="1" t="str">
+      <c r="H7" t="str">
         <v>08-Pictures/CASA GLASS OAK</v>
       </c>
-      <c r="I7" s="1" t="str">
+      <c r="I7" t="str">
         <v>FRONT-01-3D.webp</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="str">
-        <v>LAKE WORTH MEDICAL OFFICE BUILDING</v>
-      </c>
-      <c r="C8" s="1" t="str">
+      <c r="B8" t="str">
+        <v>3500 OFFICE PROFESSIONAL BUILDING</v>
+      </c>
+      <c r="C8" t="str">
         <v>lake-worth-medical-office-building</v>
       </c>
-      <c r="D8" s="1" t="str">
+      <c r="D8" t="str">
         <v>Design Tech International</v>
       </c>
-      <c r="E8" s="1" t="str">
-        <v>Structural design engineering services for a three-story medical building, including the urgent care and MRI center.</v>
-      </c>
-      <c r="F8" s="1" t="str">
-        <v>Palm Beach, FL</v>
-      </c>
-      <c r="G8" s="1" t="str">
+      <c r="E8" t="str">
+        <v>Structural design engineering services for a two-story medical building, including the urgent care and MRI center.</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Miami, FL</v>
+      </c>
+      <c r="G8" t="str">
         <v>COMMERCIAL</v>
       </c>
-      <c r="H8" s="1" t="str">
+      <c r="H8" t="str">
         <v>08-Pictures/LAKE WORTH MEDICAL OFFICE BUILDING</v>
       </c>
-      <c r="I8" s="1" t="str">
+      <c r="I8" t="str">
         <v>Picture6.webp</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="str">
+      <c r="B9" t="str">
         <v>EAST 49 STREET</v>
       </c>
-      <c r="C9" s="1" t="str">
+      <c r="C9" t="str">
         <v>east-49-street</v>
       </c>
-      <c r="D9" s="1" t="str">
+      <c r="D9" t="str">
         <v>Design Tech International</v>
       </c>
-      <c r="E9" s="1" t="str">
+      <c r="E9" t="str">
         <v>Structural design engineering services for a three-story apartment building.</v>
       </c>
-      <c r="F9" s="1" t="str">
+      <c r="F9" t="str">
         <v>Hialeah, FL</v>
       </c>
-      <c r="G9" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H9" s="1" t="str">
+      <c r="G9" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H9" t="str">
         <v>08-Pictures/EAST 49 STREET</v>
       </c>
-      <c r="I9" s="1" t="str">
+      <c r="I9" t="str">
         <v>Final - Front.webp</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="str">
+      <c r="B10" t="str">
         <v>CITY VISTA</v>
       </c>
-      <c r="C10" s="1" t="str">
+      <c r="C10" t="str">
         <v>city-vista</v>
       </c>
-      <c r="D10" s="1" t="str">
+      <c r="D10" t="str">
         <v>Corwil Architects</v>
       </c>
-      <c r="E10" s="1" t="str">
+      <c r="E10" t="str">
         <v>Structural design engineering services for a seven-story apartment building.</v>
       </c>
-      <c r="F10" s="1" t="str">
+      <c r="F10" t="str">
         <v>Pompano Beach, FL</v>
       </c>
-      <c r="G10" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H10" s="1" t="str">
+      <c r="G10" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H10" t="str">
         <v>08-Pictures/CITY VISTA</v>
       </c>
-      <c r="I10" s="1" t="str">
+      <c r="I10" t="str">
         <v>2022-08-14 (2).webp</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="str">
+      <c r="B11" t="str">
         <v>BAHAMA BAY 3</v>
       </c>
-      <c r="C11" s="1" t="str">
+      <c r="C11" t="str">
         <v>bahama-bay-3</v>
       </c>
-      <c r="D11" s="1" t="str">
+      <c r="D11" t="str">
         <v>WHA Design</v>
       </c>
-      <c r="E11" s="1" t="str">
+      <c r="E11" t="str">
         <v>Structural design engineering services for a two-story multi-family residential building.</v>
       </c>
-      <c r="F11" s="1" t="str">
+      <c r="F11" t="str">
         <v>BAHAM BAY 3</v>
       </c>
-      <c r="G11" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H11" s="1" t="str">
+      <c r="G11" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H11" t="str">
         <v>08-Pictures/BAHAM BAY 3</v>
       </c>
-      <c r="I11" s="1" t="str">
+      <c r="I11" t="str">
         <v>Picture7.webp</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="str">
+      <c r="B12" t="str">
         <v>“O” RESIDENCE</v>
       </c>
-      <c r="C12" s="1" t="str">
+      <c r="C12" t="str">
         <v>o-residence</v>
       </c>
-      <c r="D12" s="1" t="str">
+      <c r="D12" t="str">
         <v>Charles Benson &amp; Associates</v>
       </c>
-      <c r="E12" s="1" t="str">
+      <c r="E12" t="str">
         <v>Structural design engineering services for a Nine-story condominium, including a two-story parking garage and pool deck on the 3rd floor.</v>
       </c>
-      <c r="F12" s="1" t="str">
+      <c r="F12" t="str">
         <v>Bay Harbor Island, FL</v>
       </c>
-      <c r="G12" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H12" s="1" t="str">
+      <c r="G12" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H12" t="str">
         <v>08-Pictures/O RESIDENCE</v>
       </c>
-      <c r="I12" s="1" t="str">
+      <c r="I12" t="str">
         <v>Picture8.webp</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="str">
+      <c r="B13" t="str">
         <v>IVORY CONDOMINIUM</v>
       </c>
-      <c r="C13" s="1" t="str">
+      <c r="C13" t="str">
         <v>ivory-condominium</v>
       </c>
-      <c r="D13" s="1" t="str">
+      <c r="D13" t="str">
         <v>Frankel Benayoun Architects Inc.</v>
       </c>
-      <c r="E13" s="1" t="str">
+      <c r="E13" t="str">
         <v>Structural design engineering services for a Nine-story condominium, including parking spaces in the basement and pool deck at the roof level.</v>
       </c>
-      <c r="F13" s="1" t="str">
+      <c r="F13" t="str">
         <v>Bay Harbor Island, FL</v>
       </c>
-      <c r="G13" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H13" s="1" t="str">
+      <c r="G13" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H13" t="str">
         <v>08-Pictures/IVORY CONDOMINIUM</v>
       </c>
-      <c r="I13" s="1" t="str">
+      <c r="I13" t="str">
         <v>Picture9.webp</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="str">
+      <c r="B14" t="str">
         <v>RESIDENCE INN by MARRIOTT</v>
       </c>
-      <c r="C14" s="1" t="str">
+      <c r="C14" t="str">
         <v>residence-inn-by-marriott</v>
       </c>
-      <c r="D14" s="1" t="str">
+      <c r="D14" t="str">
         <v>PHILLIPS Architect</v>
       </c>
-      <c r="E14" s="1" t="str">
+      <c r="E14" t="str">
         <v>Structural design engineering services for a six-story hotel facility.</v>
       </c>
-      <c r="F14" s="1" t="str">
+      <c r="F14" t="str">
         <v>Doral, FL</v>
       </c>
-      <c r="G14" s="1" t="str">
+      <c r="G14" t="str">
         <v>COMMERCIAL</v>
       </c>
-      <c r="H14" s="1" t="str">
-        <v>08-Pictures/RESIDENCE INN BY MARRIOT</v>
-      </c>
-      <c r="I14" s="1" t="str">
+      <c r="H14" t="str">
         <v/>
       </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="str">
+      <c r="B15" t="str">
         <v>BAY HARBOR CLUB</v>
       </c>
-      <c r="C15" s="1" t="str">
+      <c r="C15" t="str">
         <v>bay-harbor-club</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D15" t="str">
         <v>Frankel Benayoun Architects Inc.</v>
       </c>
-      <c r="E15" s="1" t="str">
+      <c r="E15" t="str">
         <v>Structural design engineering services for an 8-story condominium, including parking spaces in the basement and pool deck at the roof level.</v>
       </c>
-      <c r="F15" s="1" t="str">
+      <c r="F15" t="str">
         <v>Bay Harbor Island, FL</v>
       </c>
-      <c r="G15" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H15" s="1" t="str">
+      <c r="G15" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H15" t="str">
         <v>08-Pictures/BAY HARBOR CLUB</v>
       </c>
-      <c r="I15" s="1" t="str">
+      <c r="I15" t="str">
         <v>Picture10.webp</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="str">
+      <c r="B16" t="str">
         <v>ATLANTIC HOTEL’S SHORING</v>
       </c>
-      <c r="C16" s="1" t="str">
+      <c r="C16" t="str">
         <v>atlantic-hotels-shoring</v>
       </c>
-      <c r="D16" s="1" t="str">
+      <c r="D16" t="str">
         <v>COASTAL Construction</v>
       </c>
-      <c r="E16" s="1" t="str">
+      <c r="E16" t="str">
         <v>Structural design engineering services for bracing three sides of the exterior walls of a historical building from the 2nd floor to the roof level during the construction.</v>
       </c>
-      <c r="F16" s="1" t="str">
+      <c r="F16" t="str">
         <v>Miami Beach, FL</v>
       </c>
-      <c r="G16" s="1" t="str">
+      <c r="G16" t="str">
         <v>COMMERCIAL</v>
       </c>
-      <c r="H16" s="1" t="str">
+      <c r="H16" t="str">
         <v>08-Pictures/ATLANTIC HOTELS SHORING</v>
       </c>
-      <c r="I16" s="1" t="str">
+      <c r="I16" t="str">
         <v>Picture11.webp</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="str">
+      <c r="B17" t="str">
         <v>BAY VIEW 102</v>
       </c>
-      <c r="C17" s="1" t="str">
+      <c r="C17" t="str">
         <v>bay-view-102</v>
       </c>
-      <c r="D17" s="1" t="str">
+      <c r="D17" t="str">
         <v>Frankel Benayoun Architects Inc.</v>
       </c>
-      <c r="E17" s="1" t="str">
+      <c r="E17" t="str">
         <v>Structural design engineering services for a nine-story condominium, including parking spaces in the basement and pool deck at the roof level.</v>
       </c>
-      <c r="F17" s="1" t="str">
+      <c r="F17" t="str">
         <v>Bay Harbor Island, FL</v>
       </c>
-      <c r="G17" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H17" s="1" t="str">
+      <c r="G17" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H17" t="str">
         <v>08-Pictures/BAY VIEW 102</v>
       </c>
-      <c r="I17" s="1" t="str">
+      <c r="I17" t="str">
         <v>Picture12.webp</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="str">
+      <c r="B18" t="str">
         <v>SHANTI KIDS SCHOOL</v>
       </c>
-      <c r="C18" s="1" t="str">
+      <c r="C18" t="str">
         <v>shanti-kids-school</v>
       </c>
-      <c r="D18" s="1" t="str">
+      <c r="D18" t="str">
         <v>Design Tech International/ SABI LLC</v>
       </c>
-      <c r="E18" s="1" t="str">
+      <c r="E18" t="str">
         <v>Structural design for a 2-story educational building with exterior Precast Concrete Wall.</v>
       </c>
-      <c r="F18" s="1" t="str">
+      <c r="F18" t="str">
         <v>Miami, FL</v>
       </c>
-      <c r="G18" s="1" t="str">
+      <c r="G18" t="str">
         <v>EDUCATIONAL</v>
       </c>
-      <c r="H18" s="1" t="str">
+      <c r="H18" t="str">
         <v>08-Pictures/SHANTI KIDS SCHOOL</v>
       </c>
-      <c r="I18" s="1" t="str">
+      <c r="I18" t="str">
         <v>10shell.webp</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="str">
+      <c r="B19" t="str">
         <v>JEFFERSON</v>
       </c>
-      <c r="C19" s="1" t="str">
+      <c r="C19" t="str">
         <v>jefferson</v>
       </c>
-      <c r="D19" s="1" t="str">
+      <c r="D19" t="str">
         <v>LLR ARCHITECTS,INC</v>
       </c>
-      <c r="E19" s="1" t="str">
+      <c r="E19" t="str">
+        <v>Structural design engineering services for an 8-story condominium, including a two-story parking garage.</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Hollywood, FL</v>
+      </c>
+      <c r="G19" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H19" t="str">
+        <v>08-Pictures/Jefferson</v>
+      </c>
+      <c r="I19" t="str">
+        <v>RENDER 1.webp</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>1735 JACKSON</v>
+      </c>
+      <c r="C20" t="str">
+        <v>1735-jackson</v>
+      </c>
+      <c r="D20" t="str">
+        <v>LLR ARCHITECTS,INC</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Structural design engineering services for an 9-story condominium, including a two-story parking garage.</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Hollywood, FL</v>
+      </c>
+      <c r="G20" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H20" t="str">
+        <v>08-Pictures/1735 Jackson</v>
+      </c>
+      <c r="I20" t="str">
+        <v>RENDER 1.webp</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>GRIFFING</v>
+      </c>
+      <c r="C21" t="str">
+        <v>griffing</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Design Tech International</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Structural design engineering services for an 8-story condominium, including parking spaces in the basement</v>
+      </c>
+      <c r="F21" t="str">
+        <v>North Miami, FL</v>
+      </c>
+      <c r="G21" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H21" t="str">
         <v/>
       </c>
-      <c r="F19" s="1" t="str">
+      <c r="I21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>LUDLAM PLAZA</v>
+      </c>
+      <c r="C22" t="str">
+        <v>ludlam-plaza</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Design Tech International</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Structural engineering services for a 4-story plaze with approximately 80.500 SF, including concrete and steel framing metal deck and metal joist.</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Hialeah, FL</v>
+      </c>
+      <c r="G22" t="str">
+        <v>MIX USED</v>
+      </c>
+      <c r="H22" t="str">
+        <v>08-Pictures/LUDLAM PLAZA</v>
+      </c>
+      <c r="I22" t="str">
+        <v>01.webp</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>MALL 163</v>
+      </c>
+      <c r="C23" t="str">
+        <v>mall-163</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Design Tech International</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Façade replacing and renovation</v>
+      </c>
+      <c r="F23" t="str">
+        <v>North Miami, FL</v>
+      </c>
+      <c r="G23" t="str">
+        <v>COMMERCIAL</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>LUX GROVE</v>
+      </c>
+      <c r="C24" t="str">
+        <v>lux-grove</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Design Tech International</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Structural design engineering services for multifamily development, including concrete structures with masonry walls, concrete slab floors, and gable roof.</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Homestead, FL</v>
+      </c>
+      <c r="G24" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>27</v>
+      </c>
+      <c r="B25" t="str">
+        <v>WAVE LANDING</v>
+      </c>
+      <c r="C25" t="str">
+        <v>wave-landing</v>
+      </c>
+      <c r="D25" t="str">
+        <v>AMERICAN BUILDING ENGINEERS (ABE)</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Structural design engineering services for an 6-story condominium, including parking spaces in the basement. Including pile cap foundation, concrete slab, concrete columns and shear walls</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Fort Lauderdale, FL</v>
+      </c>
+      <c r="G25" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H25" t="str">
+        <v>08-Pictures/WAVE LANDING</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Pages from APPROVED BINDER.webp</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>28</v>
+      </c>
+      <c r="B26" t="str">
+        <v>BONNER CREEK</v>
+      </c>
+      <c r="C26" t="str">
+        <v>bonner-creek</v>
+      </c>
+      <c r="D26" t="str">
+        <v>WHA Design</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Structural design engineering services for a hotel entrance with steel framing and metal deck</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Kissimee, FL</v>
+      </c>
+      <c r="G26" t="str">
+        <v>COMMERCIAL</v>
+      </c>
+      <c r="H26" t="str">
+        <v>08-Pictures/BONNER CREEK</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Rendering 1 (2).webp</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>29</v>
+      </c>
+      <c r="B27" t="str">
+        <v>1714 VAN BUREN STREET</v>
+      </c>
+      <c r="C27" t="str">
+        <v>1714-van-buren-street</v>
+      </c>
+      <c r="D27" t="str">
+        <v>LLR ARCHITECTS,INC</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
         <v>Hollywood, FL</v>
       </c>
-      <c r="G19" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H19" s="1" t="str">
-        <v>08-Pictures/Jefferson</v>
-      </c>
-      <c r="I19" s="1" t="str">
-        <v>RENDER 1.webp</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="str">
-        <v>1735 JACKSON</v>
-      </c>
-      <c r="C20" s="1" t="str">
-        <v>1735-jackson</v>
-      </c>
-      <c r="D20" s="1" t="str">
-        <v>LLR ARCHITECTS,INC</v>
-      </c>
-      <c r="E20" s="1" t="str">
+      <c r="G27" t="str">
+        <v>MULTI-FAMILY</v>
+      </c>
+      <c r="H27" t="str">
+        <v>08-Pictures/1714 VAN BUREN STREET</v>
+      </c>
+      <c r="I27" t="str">
+        <v>1.webp</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>30</v>
+      </c>
+      <c r="B28" t="str">
+        <v>BRANCHES - EBENEZER UNITED METHODIST CHURCH</v>
+      </c>
+      <c r="C28" t="str">
+        <v>branches</v>
+      </c>
+      <c r="D28" t="str">
+        <v>WHA Design</v>
+      </c>
+      <c r="E28" t="str">
         <v/>
       </c>
-      <c r="F20" s="1" t="str">
-        <v>Hollywood, FL</v>
-      </c>
-      <c r="G20" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H20" s="1" t="str">
-        <v>08-Pictures/1735 Jackson</v>
-      </c>
-      <c r="I20" s="1" t="str">
-        <v>RENDER 1.webp</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="str">
-        <v>GRIFFING</v>
-      </c>
-      <c r="C21" s="1" t="str">
-        <v>griffing</v>
-      </c>
-      <c r="D21" s="1" t="str">
-        <v>Design Tech International</v>
-      </c>
-      <c r="E21" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F21" s="1" t="str">
-        <v>North Miami, FL</v>
-      </c>
-      <c r="G21" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H21" s="1" t="str">
-        <v>08-Pictures/GRIFFIN</v>
-      </c>
-      <c r="I21" s="1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="str">
-        <v>LUDLAM PLAZA</v>
-      </c>
-      <c r="C22" s="1" t="str">
-        <v>ludlam-plaza</v>
-      </c>
-      <c r="D22" s="1" t="str">
-        <v>Design Tech International</v>
-      </c>
-      <c r="E22" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F22" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G22" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H22" s="1" t="str">
-        <v>08-Pictures/LUDLAM PLAZA</v>
-      </c>
-      <c r="I22" s="1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="str">
-        <v>MALL 163</v>
-      </c>
-      <c r="C23" s="1" t="str">
-        <v>mall-163</v>
-      </c>
-      <c r="D23" s="1" t="str">
-        <v>Design Tech International</v>
-      </c>
-      <c r="E23" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F23" s="1" t="str">
-        <v>North Miami, FL</v>
-      </c>
-      <c r="G23" s="1" t="str">
-        <v>COMMERCIAL</v>
-      </c>
-      <c r="H23" s="1" t="str">
-        <v>08-Pictures/MALL 163</v>
-      </c>
-      <c r="I23" s="1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1" t="str">
-        <v>LUX GROVE</v>
-      </c>
-      <c r="C24" s="1" t="str">
-        <v>lux-grove</v>
-      </c>
-      <c r="D24" s="1" t="str">
-        <v>Design Tech International</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F24" s="1" t="str">
-        <v>Homestead, FL</v>
-      </c>
-      <c r="G24" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H24" s="1" t="str">
-        <v>08-Pictures/LUX GROVE</v>
-      </c>
-      <c r="I24" s="1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="str">
-        <v>CASA VILLA DE LUZ</v>
-      </c>
-      <c r="C25" s="1" t="str">
-        <v>casa-villa-de-luz</v>
-      </c>
-      <c r="D25" s="1" t="str">
-        <v>FAO Architects</v>
-      </c>
-      <c r="E25" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F25" s="1" t="str">
-        <v>Pinecrest, FL</v>
-      </c>
-      <c r="G25" s="1" t="str">
-        <v>SINGLE FAMILY</v>
-      </c>
-      <c r="H25" s="1" t="str">
-        <v>08-Pictures/CASA VILLA DE LUZ</v>
-      </c>
-      <c r="I25" s="1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="str">
-        <v>CASA LAKESIDE</v>
-      </c>
-      <c r="C26" s="1" t="str">
-        <v>casa-lakeside</v>
-      </c>
-      <c r="D26" s="1" t="str">
-        <v>FAO Architects</v>
-      </c>
-      <c r="E26" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F26" s="1" t="str">
-        <v>Lakeside Dr., FL</v>
-      </c>
-      <c r="G26" s="1" t="str">
-        <v>SINGLE FAMILY</v>
-      </c>
-      <c r="H26" s="1" t="str">
-        <v>08-Pictures/CASA LAKESIDE</v>
-      </c>
-      <c r="I26" s="1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="str">
-        <v>CASA CALAIS</v>
-      </c>
-      <c r="C27" s="1" t="str">
-        <v>casa-calais</v>
-      </c>
-      <c r="D27" s="1" t="str">
-        <v>FAO Architects</v>
-      </c>
-      <c r="E27" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F27" s="1" t="str">
-        <v>Miami Beach, FL</v>
-      </c>
-      <c r="G27" s="1" t="str">
-        <v>SINGLE FAMILY</v>
-      </c>
-      <c r="H27" s="1" t="str">
-        <v>08-Pictures/CASA CALAIS</v>
-      </c>
-      <c r="I27" s="1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="str">
-        <v>WAVE LANDING</v>
-      </c>
-      <c r="C28" s="1" t="str">
-        <v>wave-landing</v>
-      </c>
-      <c r="D28" s="1" t="str">
-        <v>AMERICAN BUILDING ENGINEERS (ABE)</v>
-      </c>
-      <c r="E28" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F28" s="1" t="str">
-        <v>Fort Lauderdale, FL</v>
-      </c>
-      <c r="G28" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H28" s="1" t="str">
-        <v>08-Pictures/WAVE LANDING</v>
-      </c>
-      <c r="I28" s="1" t="str">
-        <v>Pages from APPROVED BINDER.webp</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="str">
-        <v>BONNER CREEK</v>
-      </c>
-      <c r="C29" s="1" t="str">
-        <v>bonner-creek</v>
-      </c>
-      <c r="D29" s="1" t="str">
-        <v>WHA Design</v>
-      </c>
-      <c r="E29" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F29" s="1" t="str">
-        <v>Kissimee, FL</v>
-      </c>
-      <c r="G29" s="1" t="str">
-        <v>COMMERCIAL</v>
-      </c>
-      <c r="H29" s="1" t="str">
-        <v>08-Pictures/BONNER CREEK</v>
-      </c>
-      <c r="I29" s="1" t="str">
-        <v>Rendering 1 (2).webp</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="str">
-        <v>1714 VAN BUREN STREET</v>
-      </c>
-      <c r="C30" s="1" t="str">
-        <v>1714-van-buren-street</v>
-      </c>
-      <c r="D30" s="1" t="str">
-        <v>LLR ARCHITECTS,INC</v>
-      </c>
-      <c r="E30" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F30" s="1" t="str">
-        <v>Hollywood, FL</v>
-      </c>
-      <c r="G30" s="1" t="str">
-        <v>MULTI-FAMILY</v>
-      </c>
-      <c r="H30" s="1" t="str">
-        <v>08-Pictures/1714 VAN BUREN STREET</v>
-      </c>
-      <c r="I30" s="1" t="str">
-        <v>1714 VAN BUREN STREET ARCHITECTURE- Page 017.webp</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1" t="str">
-        <v>BRUNCHES</v>
-      </c>
-      <c r="C31" s="1" t="str">
-        <v>brunches</v>
-      </c>
-      <c r="D31" s="1" t="str">
-        <v/>
-      </c>
-      <c r="E31" s="1" t="str">
-        <v/>
-      </c>
-      <c r="F31" s="1" t="str">
-        <v/>
-      </c>
-      <c r="G31" s="1" t="str">
-        <v/>
-      </c>
-      <c r="H31" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I31" s="1" t="str">
-        <v/>
+      <c r="F28" t="str">
+        <v>Miami, FL</v>
+      </c>
+      <c r="G28" t="str">
+        <v>EDUCATIONAL</v>
+      </c>
+      <c r="H28" t="str">
+        <v>08-Pictures/BRANCHES</v>
+      </c>
+      <c r="I28" t="str">
+        <v>RENDERING 01 6.webp</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/assets/files/catalog.xlsx
+++ b/src/assets/files/catalog.xlsx
@@ -1002,10 +1002,10 @@
         <v>MULTI-FAMILY</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>08-Pictures/GRIFFIN</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>01-PRINCIPAL-new.webp</v>
       </c>
     </row>
     <row r="22">
@@ -1060,10 +1060,10 @@
         <v>COMMERCIAL</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>08-Pictures/MALL 163</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>01.webp</v>
       </c>
     </row>
     <row r="24">
@@ -1089,10 +1089,10 @@
         <v>MULTI-FAMILY</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>08-Pictures/LUX GROVE</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>01-PRINCIPAL.webp</v>
       </c>
     </row>
     <row r="25">
@@ -1167,7 +1167,7 @@
         <v>LLR ARCHITECTS,INC</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>Structural design engineering services for 10 units multi-family development. Including a concrete structure with a precast joist and a concrete shear wall.</v>
       </c>
       <c r="F27" t="str">
         <v>Hollywood, FL</v>
@@ -1196,7 +1196,7 @@
         <v>WHA Design</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>Structural design engineering services for renovating and adding to the existing church, including new educational spaces and multipurpose rooms, in combination with a steel and masonry structure with metal joists and a concrete roof.</v>
       </c>
       <c r="F28" t="str">
         <v>Miami, FL</v>
